--- a/diseases/d203/2000-2004.xlsx
+++ b/diseases/d203/2000-2004.xlsx
@@ -768,11 +768,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>SER_PL_ECDC_CCHF_ANNUAL</t>
@@ -790,12 +785,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -806,11 +796,6 @@
       <c r="AT2" t="n">
         <v>1</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -875,7 +860,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -910,12 +895,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -924,99 +909,19 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>SER_PL_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_CCHF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>SRC_PL_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Crimean-Congo haemorrhagic fever</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>country:PL:national</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN3" t="b">
-        <v>1</v>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1024,12 +929,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1040,11 +940,6 @@
       <c r="AT3" t="n">
         <v>1</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -1081,399 +976,6 @@
         </is>
       </c>
       <c r="BC3" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>D203</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>crimean-congo-hemorrhagic-fever</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Crimean-Congo hemorrhagic fever</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>D203</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Crimean-Congo hemorrhagic fever</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>克里米亚-刚果出血热</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2004-01</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_CCHF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_CCHF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>D203</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>crimean-congo-hemorrhagic-fever</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Crimean-Congo hemorrhagic fever</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>D203</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Crimean-Congo hemorrhagic fever</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>克里米亚-刚果出血热</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2004-01</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_CCHF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_CCHF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>SRC_PL_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Crimean-Congo haemorrhagic fever</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>country:PL:national</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_CCHF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -1605,7 +1107,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1625,7 +1127,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1635,7 +1137,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d203/2000-2004.xlsx
+++ b/diseases/d203/2000-2004.xlsx
@@ -768,6 +768,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>SER_PL_ECDC_CCHF_ANNUAL</t>
@@ -785,7 +790,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -796,6 +806,11 @@
       <c r="AT2" t="n">
         <v>1</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -860,7 +875,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -895,12 +910,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -909,19 +924,99 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>SER_PL_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_CCHF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_PL_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Crimean-Congo haemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:PL:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -929,7 +1024,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -940,6 +1040,11 @@
       <c r="AT3" t="n">
         <v>1</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -976,6 +1081,399 @@
         </is>
       </c>
       <c r="BC3" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D203</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>crimean-congo-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Crimean-Congo hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>D203</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Crimean-Congo hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>克里米亚-刚果出血热</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_CCHF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_CCHF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D203</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>crimean-congo-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Crimean-Congo hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>D203</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Crimean-Congo hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>克里米亚-刚果出血热</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_CCHF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_CCHF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_PL_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Crimean-Congo haemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:PL:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_CCHF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -1107,7 +1605,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1127,7 +1625,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1137,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
